--- a/frontend/public/csvTemplate.xlsx
+++ b/frontend/public/csvTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\My History of Scouting\Repository\my_history_v2\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3B7F9B-F6C1-4495-BA9C-7C7E4BB44494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6E47D1-D6E7-49F9-A9D8-B4DA852F0C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{3F548D7E-695F-4EE2-9F46-D9719D78BBA0}"/>
+    <workbookView xWindow="10605" yWindow="0" windowWidth="18300" windowHeight="17385" xr2:uid="{3F548D7E-695F-4EE2-9F46-D9719D78BBA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
   <si>
     <t>ユニークID</t>
     <phoneticPr fontId="1"/>
@@ -378,12 +378,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>bvs:ビーバー,cs:カブ
-bs:ボーイ,vs:ベンチャー
-rs:ローバー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>技能章の名前、取得日、考査員名を半角ピリオドで区切る(名前以外省略可)。複数個はそれぞれ半角セミコロンで区切る。</t>
     <rPh sb="0" eb="2">
       <t>ギノウ</t>
@@ -466,6 +460,45 @@
     <t>〇公園</t>
     <rPh sb="1" eb="3">
       <t>コウエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bvs:ビーバー,cs:カブ
+bs:ボーイ,vs:ベンチャー
+rs:ローバー,ob:既卒</t>
+    <rPh sb="42" eb="44">
+      <t>キソツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名称~開始日時~終了日時</t>
+    <rPh sb="0" eb="2">
+      <t>メイショウ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>カイシニチジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ニチジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>リーダー~2015-10-10~2015-10-10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進級:ビーバー</t>
+    <rPh sb="0" eb="2">
+      <t>シンキュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -584,122 +617,83 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1039,477 +1033,450 @@
   <dimension ref="A1:AK8"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="24.625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="23" style="15" customWidth="1"/>
-    <col min="3" max="3" width="16.875" style="16" customWidth="1"/>
-    <col min="4" max="4" width="17.5" style="16" customWidth="1"/>
-    <col min="5" max="5" width="13.5" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.625" style="16" customWidth="1"/>
-    <col min="7" max="7" width="24.125" style="16" customWidth="1"/>
-    <col min="8" max="8" width="39.25" style="16" customWidth="1"/>
-    <col min="9" max="9" width="40.125" style="17" customWidth="1"/>
-    <col min="10" max="10" width="9.375" style="18" customWidth="1"/>
-    <col min="11" max="11" width="12.75" style="18" customWidth="1"/>
-    <col min="12" max="12" width="13.125" style="18" customWidth="1"/>
-    <col min="13" max="13" width="9.375" style="19" customWidth="1"/>
-    <col min="14" max="14" width="14" style="19" customWidth="1"/>
-    <col min="15" max="15" width="12.75" style="19" customWidth="1"/>
-    <col min="16" max="16" width="5.25" style="20" customWidth="1"/>
-    <col min="17" max="17" width="13.375" style="20" customWidth="1"/>
-    <col min="18" max="21" width="9" style="16"/>
-    <col min="22" max="25" width="9" style="21"/>
-    <col min="26" max="29" width="9" style="17"/>
-    <col min="30" max="33" width="9" style="22"/>
-    <col min="34" max="37" width="9" style="19"/>
-    <col min="38" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="24.625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23" style="4" customWidth="1"/>
+    <col min="3" max="3" width="16.875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" style="5" customWidth="1"/>
+    <col min="5" max="5" width="13.5" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="24.125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="39.25" style="5" customWidth="1"/>
+    <col min="9" max="9" width="40.125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="13" style="7" customWidth="1"/>
+    <col min="11" max="11" width="8.125" style="7" customWidth="1"/>
+    <col min="12" max="12" width="8.75" style="7" customWidth="1"/>
+    <col min="13" max="13" width="13.125" style="8" customWidth="1"/>
+    <col min="14" max="14" width="11.125" style="8" customWidth="1"/>
+    <col min="15" max="15" width="8.625" style="8" customWidth="1"/>
+    <col min="16" max="16" width="12.625" style="9" customWidth="1"/>
+    <col min="17" max="17" width="8.625" style="9" customWidth="1"/>
+    <col min="18" max="18" width="9" style="5"/>
+    <col min="19" max="19" width="12.625" style="5" customWidth="1"/>
+    <col min="20" max="20" width="32.375" style="5" customWidth="1"/>
+    <col min="21" max="21" width="17.125" style="5" customWidth="1"/>
+    <col min="22" max="25" width="9" style="10"/>
+    <col min="26" max="29" width="9" style="6"/>
+    <col min="30" max="33" width="9" style="11"/>
+    <col min="34" max="37" width="9" style="8"/>
+    <col min="38" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:37" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" s="24" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:37" ht="72" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="23"/>
-      <c r="AA2" s="23"/>
-      <c r="AB2" s="23"/>
-      <c r="AC2" s="23"/>
-      <c r="AD2" s="23"/>
-      <c r="AE2" s="23"/>
-      <c r="AF2" s="23"/>
-      <c r="AG2" s="23"/>
-      <c r="AH2" s="23"/>
-      <c r="AI2" s="23"/>
-      <c r="AJ2" s="23"/>
-      <c r="AK2" s="23"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3"/>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.4">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="2"/>
+      <c r="AE3" s="2"/>
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="2"/>
+      <c r="AH3" s="2"/>
+      <c r="AI3" s="2"/>
+      <c r="AJ3" s="2"/>
+      <c r="AK3" s="2"/>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.4">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="5"/>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="5"/>
-      <c r="AK4" s="5"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="24"/>
+      <c r="C5" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="9" t="s">
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="10" t="s">
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="11" t="s">
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="7" t="s">
+      <c r="Q5" s="22"/>
+      <c r="R5" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="12" t="s">
+      <c r="S5" s="23"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="V5" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="13" t="s">
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="14" t="s">
+      <c r="AA5" s="17"/>
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="AE5" s="14"/>
-      <c r="AF5" s="14"/>
-      <c r="AG5" s="14"/>
-      <c r="AH5" s="10" t="s">
+      <c r="AE5" s="18"/>
+      <c r="AF5" s="18"/>
+      <c r="AG5" s="18"/>
+      <c r="AH5" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="AI5" s="10"/>
-      <c r="AJ5" s="10"/>
-      <c r="AK5" s="10"/>
+      <c r="AI5" s="19"/>
+      <c r="AJ5" s="19"/>
+      <c r="AK5" s="19"/>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.4">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="I6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="18" t="s">
+      <c r="M6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="19" t="s">
+      <c r="N6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="O6" s="19" t="s">
+      <c r="P6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="P6" s="20" t="s">
+      <c r="Q6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q6" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="R6" s="16" t="s">
+      <c r="R6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="16" t="s">
+      <c r="S6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="T6" s="16" t="s">
+      <c r="T6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="U6" s="16" t="s">
+      <c r="U6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="V6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="W6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="X6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="V6" s="21" t="s">
+      <c r="Z6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="W6" s="21" t="s">
+      <c r="AA6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="X6" s="21" t="s">
+      <c r="AB6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Y6" s="21" t="s">
+      <c r="AC6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="Z6" s="17" t="s">
+      <c r="AD6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AA6" s="17" t="s">
+      <c r="AE6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="AB6" s="17" t="s">
+      <c r="AF6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="AC6" s="17" t="s">
+      <c r="AG6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="AD6" s="22" t="s">
+      <c r="AH6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="AE6" s="22" t="s">
+      <c r="AI6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="AF6" s="22" t="s">
+      <c r="AJ6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="AG6" s="22" t="s">
+      <c r="AK6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AH6" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI6" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ6" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="AK6" s="19" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="7" spans="1:37" s="35" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="26" t="s">
+    <row r="7" spans="1:37" ht="42.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="J7" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="I7" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7" s="30" t="s">
+      <c r="L7" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="37" t="s">
+      <c r="O7" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="P7" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="M7" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="N7" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="O7" s="38" t="s">
+      <c r="Q7" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="S7" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="32"/>
-      <c r="R7" s="27"/>
-      <c r="S7" s="27"/>
-      <c r="T7" s="27"/>
-      <c r="U7" s="27"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="33"/>
-      <c r="Y7" s="33"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="29"/>
-      <c r="AC7" s="29"/>
-      <c r="AD7" s="34"/>
-      <c r="AE7" s="34"/>
-      <c r="AF7" s="34"/>
-      <c r="AG7" s="34"/>
-      <c r="AH7" s="31"/>
-      <c r="AI7" s="31"/>
-      <c r="AJ7" s="31"/>
-      <c r="AK7" s="31"/>
+      <c r="T7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="U7" s="12"/>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.4">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="5">
         <v>12345678901</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="18" t="s">
+      <c r="I8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" s="18" t="s">
+      <c r="M8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="S8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M8" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="N8" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="P8" s="20" t="s">
-        <v>14</v>
+      <c r="T8" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
